--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED20.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED20.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>173W</t>
+          <t>204W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0080</t>
+          <t>SIM_XA_FIXED-2-0110</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29W</t>
+          <t>133W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3季</t>
+          <t>0季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1748,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0103</t>
+          <t>SIM_XA_FIXED-4-0066</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1769,11 +1769,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104W</t>
+          <t>35W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>2季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G56"/>
+  <dimension ref="B2:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>-15</v>
       </c>
       <c r="E20" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-8</v>
+        <v>-48</v>
       </c>
       <c r="E23" t="n">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E24" t="n">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-7385e7aad2", "line_id": "L-ef25ab39be", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2423,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E25" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>361</v>
+        <v>309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-14c2a4f89f", "line_id": "L-ef25ab39be", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
         <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2501,14 +2501,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>133</v>
       </c>
       <c r="E28" t="n">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0110", "receivable_term_quarters": 0, "revenue_wan": 133.0}</t>
         </is>
       </c>
     </row>
@@ -2527,23 +2527,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="E29" t="n">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0080", "receivable_term_quarters": 3, "revenue_wan": 29.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2553,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-12</v>
+        <v>-32</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-49870c6d1d", "line_id": "L-ef25ab39be", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2579,23 +2579,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-50cf7f8c24", "line_id": "L-ef25ab39be", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>-15</v>
       </c>
       <c r="E33" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E36" t="n">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2787,23 +2787,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-1a4634ab28"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2813,23 +2813,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0066", "receivable_term_quarters": 2, "revenue_wan": 35.0}</t>
         </is>
       </c>
     </row>
@@ -2839,14 +2839,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2865,14 +2865,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="E42" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-3040dde11a", "line_id": "L-ef25ab39be", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>maintenance_expense | {"line_id": "L-ef25ab39be"}</t>
         </is>
       </c>
     </row>
@@ -2891,14 +2891,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ef25ab39be", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-ef25ab39be"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ef25ab39be", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2943,23 +2943,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E45" t="n">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ef25ab39be", "asset_type": "factory"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2969,23 +2969,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ef25ab39be", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-8</v>
+        <v>35</v>
       </c>
       <c r="E47" t="n">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>receivable_collected | {"receivable_id": "AR-3619559d2e"}</t>
         </is>
       </c>
     </row>
@@ -3028,11 +3028,11 @@
         <v>-14</v>
       </c>
       <c r="E48" t="n">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>104</v>
+        <v>-14</v>
       </c>
       <c r="E49" t="n">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0103", "receivable_term_quarters": 0, "revenue_wan": 104.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3073,23 +3073,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-36</v>
+        <v>-15</v>
       </c>
       <c r="E50" t="n">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>maintenance_expense | {"line_id": "L-ef25ab39be"}</t>
         </is>
       </c>
     </row>
@@ -3099,23 +3099,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-e01568039a", "line_id": "L-ef25ab39be", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ef25ab39be", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3125,125 +3125,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E53" t="n">
-        <v>188</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E54" t="n">
-        <v>173</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-ef25ab39be"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>173</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ef25ab39be", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>53</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>173</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ef25ab39be", "asset_type": "production_line"}</t>
         </is>
@@ -3350,16 +3246,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3575,16 +3471,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3640,13 +3536,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3665,13 +3561,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" t="n">
         <v>20</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3690,13 +3586,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3712,16 +3608,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -3737,16 +3633,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-79</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>-70</v>
+        <v>-22</v>
       </c>
       <c r="G20" t="n">
-        <v>-79</v>
+        <v>-60</v>
       </c>
       <c r="H20" t="n">
-        <v>-21</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="21">
@@ -3787,16 +3683,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-94.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-85.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-94.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-36.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="23">
@@ -3837,16 +3733,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-104.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-85.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-94.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-36.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="25">
@@ -3887,16 +3783,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-104.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-85.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-94.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-36.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="28">
@@ -3986,16 +3882,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F30" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="G30" t="n">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="H30" t="n">
-        <v>173</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31">
@@ -4014,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4039,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4064,10 +3960,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H33" t="n">
         <v>60</v>
@@ -4111,16 +4007,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F35" t="n">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="G35" t="n">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="H35" t="n">
-        <v>233</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36">
@@ -4236,16 +4132,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>484.6</v>
+        <v>488.6</v>
       </c>
       <c r="F40" t="n">
-        <v>399.4</v>
+        <v>451.4</v>
       </c>
       <c r="G40" t="n">
-        <v>305.2</v>
+        <v>376.2</v>
       </c>
       <c r="H40" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
@@ -4414,13 +4310,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-190.4</v>
+        <v>-186.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-275.6</v>
+        <v>-223.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-369.8</v>
+        <v>-298.8</v>
       </c>
     </row>
     <row r="48">
@@ -4436,16 +4332,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-104.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-85.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-94.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-36.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="49">
@@ -4461,16 +4357,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>484.6</v>
+        <v>488.6</v>
       </c>
       <c r="F49" t="n">
-        <v>399.4</v>
+        <v>451.4</v>
       </c>
       <c r="G49" t="n">
-        <v>305.2</v>
+        <v>376.2</v>
       </c>
       <c r="H49" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50">
@@ -4486,16 +4382,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>484.6</v>
+        <v>488.6</v>
       </c>
       <c r="F50" t="n">
-        <v>399.4</v>
+        <v>451.4</v>
       </c>
       <c r="G50" t="n">
-        <v>305.2</v>
+        <v>376.2</v>
       </c>
       <c r="H50" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4566,7 +4462,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4715,7 +4611,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4864,7 +4760,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5013,7 +4909,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5162,7 +5058,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
